--- a/wildlife/reports/United-Kingdom/heatmap/2025/Oxford/Birds/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Oxford/Birds/heatmap.xlsx
@@ -523,7 +523,7 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -1082,7 +1082,7 @@
         <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Oxford/Birds/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Oxford/Birds/heatmap.xlsx
@@ -526,7 +526,7 @@
         <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1214,7 +1214,7 @@
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Oxford/Birds/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Oxford/Birds/heatmap.xlsx
@@ -523,10 +523,10 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1211,10 +1211,10 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1512,10 +1512,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Oxford/Birds/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Oxford/Birds/heatmap.xlsx
@@ -523,10 +523,10 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1211,10 +1211,10 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1512,10 +1512,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
